--- a/2018/South1/South1_members_final.xlsx
+++ b/2018/South1/South1_members_final.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>التنظيم الشعبي الناصري</t>
         </is>
       </c>
     </row>
